--- a/Deliverables/BOM/eSpark_BOM.xlsx
+++ b/Deliverables/BOM/eSpark_BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ezlo-irblaster\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3093C209-D5AD-4A8C-9937-46AC2D458A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F211018B-AAB7-401B-B048-0EA0B5E55D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5865" yWindow="3345" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="20 Boards" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="212">
   <si>
     <t>Component list</t>
   </si>
@@ -1162,7 +1162,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1314,6 +1314,106 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1345,108 +1445,6 @@
     <xf numFmtId="0" fontId="20" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="15" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1932,15 +1930,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="58"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="92"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1990,7 +1988,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="59"/>
+      <c r="S3" s="93"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -2015,7 +2013,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="60"/>
+      <c r="S4" s="94"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -2040,7 +2038,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="60"/>
+      <c r="S5" s="94"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -2061,7 +2059,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="60"/>
+      <c r="S6" s="94"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -2082,7 +2080,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="60"/>
+      <c r="S7" s="94"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -2103,7 +2101,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="60"/>
+      <c r="S8" s="94"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -2134,13 +2132,13 @@
       <c r="J9" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="K9" s="69" t="s">
+      <c r="K9" s="59" t="s">
         <v>177</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="M9" s="72" t="s">
+      <c r="M9" s="62" t="s">
         <v>178</v>
       </c>
       <c r="N9" s="31" t="s">
@@ -2168,7 +2166,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="66" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="45" t="s">
@@ -2192,7 +2190,7 @@
       <c r="J10" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="K10" s="70" t="s">
+      <c r="K10" s="60" t="s">
         <v>157</v>
       </c>
       <c r="L10" s="45">
@@ -2205,7 +2203,7 @@
       <c r="N10" s="45">
         <v>60</v>
       </c>
-      <c r="O10" s="78" t="s">
+      <c r="O10" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P10" s="50">
@@ -2224,7 +2222,7 @@
         <f t="shared" ref="B11:B37" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="77" t="s">
+      <c r="C11" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="48" t="s">
@@ -2236,7 +2234,7 @@
       <c r="F11" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="80" t="s">
+      <c r="G11" s="70" t="s">
         <v>97</v>
       </c>
       <c r="H11" s="48" t="s">
@@ -2248,7 +2246,7 @@
       <c r="J11" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="K11" s="71" t="s">
+      <c r="K11" s="61" t="s">
         <v>158</v>
       </c>
       <c r="L11" s="48">
@@ -2261,7 +2259,7 @@
       <c r="N11" s="48">
         <v>100</v>
       </c>
-      <c r="O11" s="79" t="s">
+      <c r="O11" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P11" s="51">
@@ -2280,7 +2278,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="66" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="45" t="s">
@@ -2302,10 +2300,10 @@
       <c r="J12" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="K12" s="70" t="s">
+      <c r="K12" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="L12" s="74">
+      <c r="L12" s="64">
         <v>1</v>
       </c>
       <c r="M12" s="45">
@@ -2315,7 +2313,7 @@
       <c r="N12" s="45">
         <v>100</v>
       </c>
-      <c r="O12" s="78" t="s">
+      <c r="O12" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P12" s="50">
@@ -2334,7 +2332,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="48" t="s">
@@ -2358,7 +2356,7 @@
       <c r="J13" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="K13" s="71" t="s">
+      <c r="K13" s="61" t="s">
         <v>160</v>
       </c>
       <c r="L13" s="48">
@@ -2371,7 +2369,7 @@
       <c r="N13" s="48">
         <v>60</v>
       </c>
-      <c r="O13" s="79" t="s">
+      <c r="O13" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P13" s="51">
@@ -2390,7 +2388,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="66" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="45" t="s">
@@ -2414,10 +2412,10 @@
       <c r="J14" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="K14" s="70" t="s">
+      <c r="K14" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="L14" s="74">
+      <c r="L14" s="64">
         <v>1</v>
       </c>
       <c r="M14" s="45">
@@ -2427,7 +2425,7 @@
       <c r="N14" s="45">
         <v>40</v>
       </c>
-      <c r="O14" s="78" t="s">
+      <c r="O14" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P14" s="50">
@@ -2446,7 +2444,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="77" t="s">
+      <c r="C15" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="48" t="s">
@@ -2458,7 +2456,7 @@
       <c r="F15" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="80" t="s">
+      <c r="G15" s="70" t="s">
         <v>100</v>
       </c>
       <c r="H15" s="48" t="s">
@@ -2470,7 +2468,7 @@
       <c r="J15" s="48" t="s">
         <v>194</v>
       </c>
-      <c r="K15" s="71" t="s">
+      <c r="K15" s="61" t="s">
         <v>162</v>
       </c>
       <c r="L15" s="48">
@@ -2483,7 +2481,7 @@
       <c r="N15" s="48">
         <v>40</v>
       </c>
-      <c r="O15" s="79" t="s">
+      <c r="O15" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P15" s="51">
@@ -2502,7 +2500,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="66" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="45" t="s">
@@ -2524,10 +2522,10 @@
       <c r="J16" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="K16" s="70" t="s">
+      <c r="K16" s="60" t="s">
         <v>163</v>
       </c>
-      <c r="L16" s="74">
+      <c r="L16" s="64">
         <v>1</v>
       </c>
       <c r="M16" s="45">
@@ -2537,7 +2535,7 @@
       <c r="N16" s="45">
         <v>50</v>
       </c>
-      <c r="O16" s="78" t="s">
+      <c r="O16" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P16" s="50">
@@ -2556,7 +2554,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="77" t="s">
+      <c r="C17" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="48" t="s">
@@ -2580,7 +2578,7 @@
       <c r="J17" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="K17" s="71" t="s">
+      <c r="K17" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L17" s="48">
@@ -2602,7 +2600,7 @@
       <c r="Q17" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="R17" s="81" t="s">
+      <c r="R17" s="71" t="s">
         <v>198</v>
       </c>
       <c r="S17" s="51"/>
@@ -2613,7 +2611,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="66" t="s">
         <v>171</v>
       </c>
       <c r="D18" s="45" t="s">
@@ -2637,10 +2635,10 @@
       <c r="J18" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="K18" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L18" s="74">
+      <c r="K18" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L18" s="64">
         <v>1</v>
       </c>
       <c r="M18" s="45">
@@ -2650,7 +2648,7 @@
       <c r="N18" s="45">
         <v>25</v>
       </c>
-      <c r="O18" s="78" t="s">
+      <c r="O18" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P18" s="50">
@@ -2669,7 +2667,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="67" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="48" t="s">
@@ -2693,7 +2691,7 @@
       <c r="J19" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="K19" s="71" t="s">
+      <c r="K19" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L19" s="48">
@@ -2706,7 +2704,7 @@
       <c r="N19" s="48">
         <v>25</v>
       </c>
-      <c r="O19" s="79" t="s">
+      <c r="O19" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P19" s="51">
@@ -2725,7 +2723,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="66" t="s">
         <v>172</v>
       </c>
       <c r="D20" s="45" t="s">
@@ -2749,10 +2747,10 @@
       <c r="J20" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="K20" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L20" s="74">
+      <c r="K20" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L20" s="64">
         <v>1</v>
       </c>
       <c r="M20" s="45">
@@ -2762,7 +2760,7 @@
       <c r="N20" s="45">
         <v>25</v>
       </c>
-      <c r="O20" s="78" t="s">
+      <c r="O20" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P20" s="50">
@@ -2781,7 +2779,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="77" t="s">
+      <c r="C21" s="67" t="s">
         <v>173</v>
       </c>
       <c r="D21" s="48" t="s">
@@ -2805,7 +2803,7 @@
       <c r="J21" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="K21" s="71" t="s">
+      <c r="K21" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L21" s="48">
@@ -2827,7 +2825,7 @@
       <c r="Q21" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="R21" s="81" t="s">
+      <c r="R21" s="71" t="s">
         <v>198</v>
       </c>
       <c r="S21" s="51"/>
@@ -2838,7 +2836,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="76" t="s">
+      <c r="C22" s="66" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="45" t="s">
@@ -2862,10 +2860,10 @@
       <c r="J22" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="K22" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L22" s="74">
+      <c r="K22" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L22" s="64">
         <v>1</v>
       </c>
       <c r="M22" s="45">
@@ -2875,7 +2873,7 @@
       <c r="N22" s="45">
         <v>30</v>
       </c>
-      <c r="O22" s="78" t="s">
+      <c r="O22" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P22" s="50">
@@ -2894,7 +2892,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="77" t="s">
+      <c r="C23" s="67" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="48" t="s">
@@ -2906,7 +2904,7 @@
       <c r="F23" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="80" t="s">
+      <c r="G23" s="70" t="s">
         <v>106</v>
       </c>
       <c r="H23" s="48" t="s">
@@ -2918,7 +2916,7 @@
       <c r="J23" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="K23" s="71" t="s">
+      <c r="K23" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L23" s="48">
@@ -2931,7 +2929,7 @@
       <c r="N23" s="48">
         <v>100</v>
       </c>
-      <c r="O23" s="79" t="s">
+      <c r="O23" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P23" s="51">
@@ -2950,7 +2948,7 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="76" t="s">
+      <c r="C24" s="66" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="45" t="s">
@@ -2968,14 +2966,16 @@
       <c r="H24" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="I24" s="45"/>
+      <c r="I24" s="45" t="s">
+        <v>175</v>
+      </c>
       <c r="J24" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="K24" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L24" s="74">
+      <c r="K24" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L24" s="64">
         <v>8</v>
       </c>
       <c r="M24" s="45">
@@ -2985,15 +2985,15 @@
       <c r="N24" s="45">
         <v>180</v>
       </c>
-      <c r="O24" s="78" t="s">
+      <c r="O24" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P24" s="50">
-        <v>4.82E-2</v>
+        <v>4.8099999999999997E-2</v>
       </c>
       <c r="Q24" s="50">
         <f t="shared" si="2"/>
-        <v>8.6760000000000002</v>
+        <v>8.6579999999999995</v>
       </c>
       <c r="R24" s="46"/>
       <c r="S24" s="50"/>
@@ -3004,7 +3004,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="77" t="s">
+      <c r="C25" s="67" t="s">
         <v>174</v>
       </c>
       <c r="D25" s="48" t="s">
@@ -3028,7 +3028,7 @@
       <c r="J25" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="K25" s="71" t="s">
+      <c r="K25" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L25" s="48">
@@ -3050,7 +3050,7 @@
       <c r="Q25" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="R25" s="81" t="s">
+      <c r="R25" s="71" t="s">
         <v>198</v>
       </c>
       <c r="S25" s="51"/>
@@ -3061,7 +3061,7 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C26" s="66" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="45" t="s">
@@ -3085,10 +3085,10 @@
       <c r="J26" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="K26" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L26" s="74">
+      <c r="K26" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L26" s="64">
         <v>1</v>
       </c>
       <c r="M26" s="45">
@@ -3098,7 +3098,7 @@
       <c r="N26" s="45">
         <v>40</v>
       </c>
-      <c r="O26" s="78" t="s">
+      <c r="O26" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P26" s="50">
@@ -3117,7 +3117,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="77" t="s">
+      <c r="C27" s="67" t="s">
         <v>12</v>
       </c>
       <c r="D27" s="48" t="s">
@@ -3129,7 +3129,7 @@
       <c r="F27" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="80" t="s">
+      <c r="G27" s="70" t="s">
         <v>109</v>
       </c>
       <c r="H27" s="48" t="s">
@@ -3141,7 +3141,7 @@
       <c r="J27" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="K27" s="71" t="s">
+      <c r="K27" s="61" t="s">
         <v>164</v>
       </c>
       <c r="L27" s="48">
@@ -3154,7 +3154,7 @@
       <c r="N27" s="48">
         <v>100</v>
       </c>
-      <c r="O27" s="79" t="s">
+      <c r="O27" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P27" s="51">
@@ -3173,7 +3173,7 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="76" t="s">
+      <c r="C28" s="66" t="s">
         <v>12</v>
       </c>
       <c r="D28" s="45" t="s">
@@ -3197,10 +3197,10 @@
       <c r="J28" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="70" t="s">
+      <c r="K28" s="60" t="s">
         <v>165</v>
       </c>
-      <c r="L28" s="74">
+      <c r="L28" s="64">
         <v>2</v>
       </c>
       <c r="M28" s="45">
@@ -3210,7 +3210,7 @@
       <c r="N28" s="45">
         <v>100</v>
       </c>
-      <c r="O28" s="78" t="s">
+      <c r="O28" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P28" s="50">
@@ -3229,7 +3229,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="77" t="s">
+      <c r="C29" s="67" t="s">
         <v>12</v>
       </c>
       <c r="D29" s="48" t="s">
@@ -3253,7 +3253,7 @@
       <c r="J29" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="K29" s="71" t="s">
+      <c r="K29" s="61" t="s">
         <v>166</v>
       </c>
       <c r="L29" s="48">
@@ -3266,7 +3266,7 @@
       <c r="N29" s="48">
         <v>100</v>
       </c>
-      <c r="O29" s="79" t="s">
+      <c r="O29" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P29" s="51">
@@ -3285,7 +3285,7 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="76" t="s">
+      <c r="C30" s="66" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="45" t="s">
@@ -3307,10 +3307,10 @@
       <c r="J30" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="K30" s="70" t="s">
+      <c r="K30" s="60" t="s">
         <v>167</v>
       </c>
-      <c r="L30" s="74">
+      <c r="L30" s="64">
         <v>2</v>
       </c>
       <c r="M30" s="45">
@@ -3320,7 +3320,7 @@
       <c r="N30" s="45">
         <v>100</v>
       </c>
-      <c r="O30" s="78" t="s">
+      <c r="O30" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P30" s="50">
@@ -3339,7 +3339,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="77" t="s">
+      <c r="C31" s="67" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="48" t="s">
@@ -3351,7 +3351,7 @@
       <c r="F31" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="G31" s="80" t="s">
+      <c r="G31" s="70" t="s">
         <v>113</v>
       </c>
       <c r="H31" s="48" t="s">
@@ -3363,7 +3363,7 @@
       <c r="J31" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="K31" s="71" t="s">
+      <c r="K31" s="61" t="s">
         <v>168</v>
       </c>
       <c r="L31" s="48">
@@ -3376,7 +3376,7 @@
       <c r="N31" s="48">
         <v>100</v>
       </c>
-      <c r="O31" s="79" t="s">
+      <c r="O31" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P31" s="51">
@@ -3395,7 +3395,7 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="76" t="s">
+      <c r="C32" s="66" t="s">
         <v>12</v>
       </c>
       <c r="D32" s="45" t="s">
@@ -3417,10 +3417,10 @@
       <c r="J32" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="K32" s="70" t="s">
+      <c r="K32" s="60" t="s">
         <v>169</v>
       </c>
-      <c r="L32" s="74">
+      <c r="L32" s="64">
         <v>1</v>
       </c>
       <c r="M32" s="45">
@@ -3430,7 +3430,7 @@
       <c r="N32" s="45">
         <v>100</v>
       </c>
-      <c r="O32" s="78" t="s">
+      <c r="O32" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P32" s="50">
@@ -3449,7 +3449,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="67" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="48" t="s">
@@ -3473,7 +3473,7 @@
       <c r="J33" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="K33" s="71" t="s">
+      <c r="K33" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L33" s="48">
@@ -3486,7 +3486,7 @@
       <c r="N33" s="48">
         <v>40</v>
       </c>
-      <c r="O33" s="79" t="s">
+      <c r="O33" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P33" s="51">
@@ -3505,7 +3505,7 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="66" t="s">
         <v>14</v>
       </c>
       <c r="D34" s="45" t="s">
@@ -3529,10 +3529,10 @@
       <c r="J34" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="K34" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L34" s="74">
+      <c r="K34" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L34" s="64">
         <v>1</v>
       </c>
       <c r="M34" s="45">
@@ -3542,7 +3542,7 @@
       <c r="N34" s="45">
         <v>22</v>
       </c>
-      <c r="O34" s="78" t="s">
+      <c r="O34" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P34" s="50">
@@ -3561,7 +3561,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="77" t="s">
+      <c r="C35" s="67" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="48" t="s">
@@ -3585,7 +3585,7 @@
       <c r="J35" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="K35" s="71" t="s">
+      <c r="K35" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L35" s="48">
@@ -3598,7 +3598,7 @@
       <c r="N35" s="48">
         <v>25</v>
       </c>
-      <c r="O35" s="79" t="s">
+      <c r="O35" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P35" s="51">
@@ -3617,7 +3617,7 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="76" t="s">
+      <c r="C36" s="66" t="s">
         <v>15</v>
       </c>
       <c r="D36" s="45" t="s">
@@ -3641,10 +3641,10 @@
       <c r="J36" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="K36" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L36" s="74">
+      <c r="K36" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L36" s="64">
         <v>1</v>
       </c>
       <c r="M36" s="45">
@@ -3654,7 +3654,7 @@
       <c r="N36" s="45">
         <v>25</v>
       </c>
-      <c r="O36" s="78" t="s">
+      <c r="O36" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P36" s="50">
@@ -3673,7 +3673,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="67" t="s">
         <v>15</v>
       </c>
       <c r="D37" s="48" t="s">
@@ -3697,10 +3697,10 @@
       <c r="J37" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="K37" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="L37" s="75">
+      <c r="K37" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="L37" s="65">
         <v>1</v>
       </c>
       <c r="M37" s="48">
@@ -3710,7 +3710,7 @@
       <c r="N37" s="48">
         <v>22</v>
       </c>
-      <c r="O37" s="79" t="s">
+      <c r="O37" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P37" s="51">
@@ -3735,19 +3735,19 @@
       <c r="I38" s="36"/>
       <c r="J38" s="35"/>
       <c r="K38" s="36"/>
-      <c r="L38" s="73"/>
+      <c r="L38" s="63"/>
       <c r="M38" s="36"/>
-      <c r="N38" s="65" t="s">
+      <c r="N38" s="99" t="s">
         <v>185</v>
       </c>
-      <c r="O38" s="66"/>
-      <c r="P38" s="66"/>
-      <c r="Q38" s="67">
+      <c r="O38" s="100"/>
+      <c r="P38" s="100"/>
+      <c r="Q38" s="57">
         <f>SUM(Q10:Q37)</f>
-        <v>123.3443</v>
-      </c>
-      <c r="R38" s="61"/>
-      <c r="S38" s="62"/>
+        <v>123.3263</v>
+      </c>
+      <c r="R38" s="95"/>
+      <c r="S38" s="96"/>
     </row>
     <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
@@ -3763,17 +3763,17 @@
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
-      <c r="N39" s="65" t="s">
+      <c r="N39" s="99" t="s">
         <v>186</v>
       </c>
-      <c r="O39" s="66"/>
-      <c r="P39" s="66"/>
-      <c r="Q39" s="68">
+      <c r="O39" s="100"/>
+      <c r="P39" s="100"/>
+      <c r="Q39" s="58">
         <f>Q38/20</f>
-        <v>6.1672150000000006</v>
-      </c>
-      <c r="R39" s="63"/>
-      <c r="S39" s="64"/>
+        <v>6.166315</v>
+      </c>
+      <c r="R39" s="97"/>
+      <c r="S39" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3792,23 +3792,23 @@
     <hyperlink ref="O19" r:id="rId6" xr:uid="{9CE8277E-0263-4BF3-8645-B6E0E9708CA2}"/>
     <hyperlink ref="O20" r:id="rId7" xr:uid="{178D71CF-40D7-4DC5-9795-FCD323285994}"/>
     <hyperlink ref="O22" r:id="rId8" xr:uid="{2AE14983-4121-4075-AA20-710E6484F95A}"/>
-    <hyperlink ref="O24" r:id="rId9" xr:uid="{AF990ABE-C9C4-4DA9-8A1D-02CA578BBA74}"/>
-    <hyperlink ref="O26" r:id="rId10" xr:uid="{40FCD2CB-2F52-4794-B790-0A06495EDAEE}"/>
-    <hyperlink ref="O28" r:id="rId11" xr:uid="{DD75499F-103A-4973-8AF4-3949C6DCA701}"/>
-    <hyperlink ref="O29" r:id="rId12" xr:uid="{504B0F06-F901-4B4A-81E5-A67FD5E85186}"/>
-    <hyperlink ref="O30" r:id="rId13" xr:uid="{A94C92B7-D7BA-4835-99E1-FD0601ADA53F}"/>
-    <hyperlink ref="O32" r:id="rId14" xr:uid="{E1A6BA6D-F21B-4C48-A35A-A78108A6C6A4}"/>
-    <hyperlink ref="O33" r:id="rId15" xr:uid="{C5D047A5-4ABA-4ABD-A149-47D71A4F2B97}"/>
-    <hyperlink ref="O34" r:id="rId16" xr:uid="{866DA471-B9D6-4C3D-9719-680D503260CC}"/>
-    <hyperlink ref="O35" r:id="rId17" xr:uid="{C871D355-E6A1-43F6-9C34-E2561F2E23CE}"/>
-    <hyperlink ref="O36" r:id="rId18" xr:uid="{765FAEE8-D833-45C8-A240-F4514C06A10E}"/>
-    <hyperlink ref="O37" r:id="rId19" xr:uid="{75C2CEFB-E28A-46C5-831C-9F3EFF39A28E}"/>
-    <hyperlink ref="O11" r:id="rId20" xr:uid="{73A50509-7619-4C9F-A0D8-44D618488429}"/>
-    <hyperlink ref="O15" r:id="rId21" xr:uid="{B49DB492-949A-4288-ABFD-BF4941C9B13F}"/>
-    <hyperlink ref="O18" r:id="rId22" xr:uid="{02F9AAAD-1AF8-4EC6-B82E-F37714D03D5E}"/>
-    <hyperlink ref="O27" r:id="rId23" xr:uid="{AED81F5F-ECAC-44CF-BF63-6E134C41DDB2}"/>
-    <hyperlink ref="O23" r:id="rId24" xr:uid="{49B5AE42-BD43-48BC-A0B4-B9B99B87E515}"/>
-    <hyperlink ref="O31" r:id="rId25" xr:uid="{DE14CB80-F4C1-4626-A341-D41C7781A31D}"/>
+    <hyperlink ref="O26" r:id="rId9" xr:uid="{40FCD2CB-2F52-4794-B790-0A06495EDAEE}"/>
+    <hyperlink ref="O28" r:id="rId10" xr:uid="{DD75499F-103A-4973-8AF4-3949C6DCA701}"/>
+    <hyperlink ref="O29" r:id="rId11" xr:uid="{504B0F06-F901-4B4A-81E5-A67FD5E85186}"/>
+    <hyperlink ref="O30" r:id="rId12" xr:uid="{A94C92B7-D7BA-4835-99E1-FD0601ADA53F}"/>
+    <hyperlink ref="O32" r:id="rId13" xr:uid="{E1A6BA6D-F21B-4C48-A35A-A78108A6C6A4}"/>
+    <hyperlink ref="O33" r:id="rId14" xr:uid="{C5D047A5-4ABA-4ABD-A149-47D71A4F2B97}"/>
+    <hyperlink ref="O34" r:id="rId15" xr:uid="{866DA471-B9D6-4C3D-9719-680D503260CC}"/>
+    <hyperlink ref="O35" r:id="rId16" xr:uid="{C871D355-E6A1-43F6-9C34-E2561F2E23CE}"/>
+    <hyperlink ref="O36" r:id="rId17" xr:uid="{765FAEE8-D833-45C8-A240-F4514C06A10E}"/>
+    <hyperlink ref="O37" r:id="rId18" xr:uid="{75C2CEFB-E28A-46C5-831C-9F3EFF39A28E}"/>
+    <hyperlink ref="O11" r:id="rId19" xr:uid="{73A50509-7619-4C9F-A0D8-44D618488429}"/>
+    <hyperlink ref="O15" r:id="rId20" xr:uid="{B49DB492-949A-4288-ABFD-BF4941C9B13F}"/>
+    <hyperlink ref="O18" r:id="rId21" xr:uid="{02F9AAAD-1AF8-4EC6-B82E-F37714D03D5E}"/>
+    <hyperlink ref="O27" r:id="rId22" xr:uid="{AED81F5F-ECAC-44CF-BF63-6E134C41DDB2}"/>
+    <hyperlink ref="O23" r:id="rId23" xr:uid="{49B5AE42-BD43-48BC-A0B4-B9B99B87E515}"/>
+    <hyperlink ref="O31" r:id="rId24" xr:uid="{DE14CB80-F4C1-4626-A341-D41C7781A31D}"/>
+    <hyperlink ref="O24" r:id="rId25" xr:uid="{65A058E1-B1EB-44DA-B3C5-01A08CE1155F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId26"/>
@@ -3852,15 +3852,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="58"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="92"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -3910,7 +3910,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="59"/>
+      <c r="S3" s="93"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -3935,7 +3935,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="60"/>
+      <c r="S4" s="94"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -3960,7 +3960,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="60"/>
+      <c r="S5" s="94"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -3981,7 +3981,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="60"/>
+      <c r="S6" s="94"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -4002,7 +4002,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="60"/>
+      <c r="S7" s="94"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -4023,7 +4023,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="60"/>
+      <c r="S8" s="94"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -4054,13 +4054,13 @@
       <c r="J9" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="K9" s="69" t="s">
+      <c r="K9" s="59" t="s">
         <v>177</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="M9" s="72" t="s">
+      <c r="M9" s="62" t="s">
         <v>201</v>
       </c>
       <c r="N9" s="31" t="s">
@@ -4082,13 +4082,13 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="82"/>
+    <row r="10" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="72"/>
       <c r="B10" s="37">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="66" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="45" t="s">
@@ -4112,7 +4112,7 @@
       <c r="J10" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="K10" s="70" t="s">
+      <c r="K10" s="60" t="s">
         <v>157</v>
       </c>
       <c r="L10" s="45">
@@ -4125,7 +4125,7 @@
       <c r="N10" s="45">
         <v>1060</v>
       </c>
-      <c r="O10" s="78" t="s">
+      <c r="O10" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P10" s="50">
@@ -4136,15 +4136,15 @@
         <v>16.535999999999998</v>
       </c>
       <c r="R10" s="46"/>
-      <c r="S10" s="83"/>
-    </row>
-    <row r="11" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="82"/>
+      <c r="S10" s="73"/>
+    </row>
+    <row r="11" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="72"/>
       <c r="B11" s="37">
         <f t="shared" ref="B11:B37" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="77" t="s">
+      <c r="C11" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="48" t="s">
@@ -4156,7 +4156,7 @@
       <c r="F11" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="80" t="s">
+      <c r="G11" s="70" t="s">
         <v>97</v>
       </c>
       <c r="H11" s="48" t="s">
@@ -4168,7 +4168,7 @@
       <c r="J11" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="K11" s="71" t="s">
+      <c r="K11" s="61" t="s">
         <v>158</v>
       </c>
       <c r="L11" s="48">
@@ -4181,7 +4181,7 @@
       <c r="N11" s="48">
         <v>2100</v>
       </c>
-      <c r="O11" s="79" t="s">
+      <c r="O11" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P11" s="51">
@@ -4194,13 +4194,13 @@
       <c r="R11" s="49"/>
       <c r="S11" s="51"/>
     </row>
-    <row r="12" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="82"/>
+    <row r="12" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="72"/>
       <c r="B12" s="37">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="66" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="45" t="s">
@@ -4222,10 +4222,10 @@
       <c r="J12" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="K12" s="70" t="s">
+      <c r="K12" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="L12" s="74">
+      <c r="L12" s="64">
         <v>1</v>
       </c>
       <c r="M12" s="45">
@@ -4235,7 +4235,7 @@
       <c r="N12" s="45">
         <v>1100</v>
       </c>
-      <c r="O12" s="78" t="s">
+      <c r="O12" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P12" s="50">
@@ -4248,13 +4248,13 @@
       <c r="R12" s="46"/>
       <c r="S12" s="50"/>
     </row>
-    <row r="13" spans="1:19" s="84" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="82"/>
+    <row r="13" spans="1:19" s="74" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="72"/>
       <c r="B13" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="48" t="s">
@@ -4278,7 +4278,7 @@
       <c r="J13" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="K13" s="71" t="s">
+      <c r="K13" s="61" t="s">
         <v>160</v>
       </c>
       <c r="L13" s="48">
@@ -4291,7 +4291,7 @@
       <c r="N13" s="48">
         <v>2060</v>
       </c>
-      <c r="O13" s="79" t="s">
+      <c r="O13" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P13" s="51">
@@ -4304,13 +4304,13 @@
       <c r="R13" s="49"/>
       <c r="S13" s="51"/>
     </row>
-    <row r="14" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="82"/>
+    <row r="14" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="72"/>
       <c r="B14" s="37">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="66" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="45" t="s">
@@ -4334,10 +4334,10 @@
       <c r="J14" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="K14" s="70" t="s">
+      <c r="K14" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="L14" s="74">
+      <c r="L14" s="64">
         <v>1</v>
       </c>
       <c r="M14" s="45">
@@ -4347,7 +4347,7 @@
       <c r="N14" s="45">
         <v>1060</v>
       </c>
-      <c r="O14" s="78" t="s">
+      <c r="O14" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P14" s="50">
@@ -4360,13 +4360,13 @@
       <c r="R14" s="46"/>
       <c r="S14" s="50"/>
     </row>
-    <row r="15" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="82"/>
+    <row r="15" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="72"/>
       <c r="B15" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="77" t="s">
+      <c r="C15" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="48" t="s">
@@ -4378,7 +4378,7 @@
       <c r="F15" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="80" t="s">
+      <c r="G15" s="70" t="s">
         <v>100</v>
       </c>
       <c r="H15" s="48" t="s">
@@ -4390,7 +4390,7 @@
       <c r="J15" s="48" t="s">
         <v>194</v>
       </c>
-      <c r="K15" s="71" t="s">
+      <c r="K15" s="61" t="s">
         <v>162</v>
       </c>
       <c r="L15" s="48">
@@ -4403,7 +4403,7 @@
       <c r="N15" s="48">
         <v>1060</v>
       </c>
-      <c r="O15" s="79" t="s">
+      <c r="O15" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P15" s="51">
@@ -4416,13 +4416,13 @@
       <c r="R15" s="49"/>
       <c r="S15" s="51"/>
     </row>
-    <row r="16" spans="1:19" s="84" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="82"/>
+    <row r="16" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="72"/>
       <c r="B16" s="37">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="76" t="s">
+      <c r="C16" s="66" t="s">
         <v>7</v>
       </c>
       <c r="D16" s="45" t="s">
@@ -4444,10 +4444,10 @@
       <c r="J16" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="K16" s="70" t="s">
+      <c r="K16" s="60" t="s">
         <v>163</v>
       </c>
-      <c r="L16" s="74">
+      <c r="L16" s="64">
         <v>1</v>
       </c>
       <c r="M16" s="45">
@@ -4457,7 +4457,7 @@
       <c r="N16" s="45">
         <v>1050</v>
       </c>
-      <c r="O16" s="78" t="s">
+      <c r="O16" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P16" s="50">
@@ -4470,13 +4470,13 @@
       <c r="R16" s="46"/>
       <c r="S16" s="50"/>
     </row>
-    <row r="17" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="82"/>
+    <row r="17" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="72"/>
       <c r="B17" s="37">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="77" t="s">
+      <c r="C17" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D17" s="48" t="s">
@@ -4500,7 +4500,7 @@
       <c r="J17" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="K17" s="71" t="s">
+      <c r="K17" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L17" s="48">
@@ -4518,18 +4518,18 @@
       <c r="Q17" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="R17" s="81" t="s">
+      <c r="R17" s="71" t="s">
         <v>198</v>
       </c>
       <c r="S17" s="51"/>
     </row>
-    <row r="18" spans="1:19" s="84" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="82"/>
+    <row r="18" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="72"/>
       <c r="B18" s="37">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="66" t="s">
         <v>171</v>
       </c>
       <c r="D18" s="45" t="s">
@@ -4553,10 +4553,10 @@
       <c r="J18" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="K18" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L18" s="74">
+      <c r="K18" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L18" s="64">
         <v>1</v>
       </c>
       <c r="M18" s="45">
@@ -4566,7 +4566,7 @@
       <c r="N18" s="45">
         <v>1050</v>
       </c>
-      <c r="O18" s="78" t="s">
+      <c r="O18" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P18" s="50">
@@ -4579,13 +4579,13 @@
       <c r="R18" s="46"/>
       <c r="S18" s="50"/>
     </row>
-    <row r="19" spans="1:19" s="84" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="82"/>
+    <row r="19" spans="1:19" s="74" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="72"/>
       <c r="B19" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="67" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="48" t="s">
@@ -4609,7 +4609,7 @@
       <c r="J19" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="K19" s="71" t="s">
+      <c r="K19" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L19" s="48">
@@ -4622,7 +4622,7 @@
       <c r="N19" s="48">
         <v>1050</v>
       </c>
-      <c r="O19" s="79" t="s">
+      <c r="O19" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P19" s="51">
@@ -4635,13 +4635,13 @@
       <c r="R19" s="49"/>
       <c r="S19" s="51"/>
     </row>
-    <row r="20" spans="1:19" s="84" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="82"/>
+    <row r="20" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="72"/>
       <c r="B20" s="37">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="66" t="s">
         <v>172</v>
       </c>
       <c r="D20" s="45" t="s">
@@ -4665,10 +4665,10 @@
       <c r="J20" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="K20" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L20" s="74">
+      <c r="K20" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L20" s="64">
         <v>1</v>
       </c>
       <c r="M20" s="45">
@@ -4678,7 +4678,7 @@
       <c r="N20" s="45">
         <v>1050</v>
       </c>
-      <c r="O20" s="78" t="s">
+      <c r="O20" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P20" s="50">
@@ -4691,13 +4691,13 @@
       <c r="R20" s="46"/>
       <c r="S20" s="50"/>
     </row>
-    <row r="21" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="82"/>
+    <row r="21" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="72"/>
       <c r="B21" s="37">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="77" t="s">
+      <c r="C21" s="67" t="s">
         <v>173</v>
       </c>
       <c r="D21" s="48" t="s">
@@ -4721,7 +4721,7 @@
       <c r="J21" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="K21" s="71" t="s">
+      <c r="K21" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L21" s="48">
@@ -4743,18 +4743,18 @@
       <c r="Q21" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="R21" s="81" t="s">
+      <c r="R21" s="71" t="s">
         <v>198</v>
       </c>
       <c r="S21" s="51"/>
     </row>
-    <row r="22" spans="1:19" s="84" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="82"/>
+    <row r="22" spans="1:19" s="74" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="72"/>
       <c r="B22" s="37">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="76" t="s">
+      <c r="C22" s="66" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="45" t="s">
@@ -4778,10 +4778,10 @@
       <c r="J22" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="K22" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L22" s="74">
+      <c r="K22" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L22" s="64">
         <v>1</v>
       </c>
       <c r="M22" s="45">
@@ -4791,7 +4791,7 @@
       <c r="N22" s="45">
         <v>1050</v>
       </c>
-      <c r="O22" s="78" t="s">
+      <c r="O22" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P22" s="50">
@@ -4804,13 +4804,13 @@
       <c r="R22" s="46"/>
       <c r="S22" s="50"/>
     </row>
-    <row r="23" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="82"/>
+    <row r="23" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="72"/>
       <c r="B23" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="77" t="s">
+      <c r="C23" s="67" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="48" t="s">
@@ -4822,7 +4822,7 @@
       <c r="F23" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="80" t="s">
+      <c r="G23" s="70" t="s">
         <v>106</v>
       </c>
       <c r="H23" s="48" t="s">
@@ -4834,7 +4834,7 @@
       <c r="J23" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="K23" s="71" t="s">
+      <c r="K23" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L23" s="48">
@@ -4847,7 +4847,7 @@
       <c r="N23" s="48">
         <v>1100</v>
       </c>
-      <c r="O23" s="79" t="s">
+      <c r="O23" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P23" s="51">
@@ -4860,13 +4860,13 @@
       <c r="R23" s="49"/>
       <c r="S23" s="51"/>
     </row>
-    <row r="24" spans="1:19" s="84" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="82"/>
+    <row r="24" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="72"/>
       <c r="B24" s="37">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="76" t="s">
+      <c r="C24" s="66" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="45" t="s">
@@ -4884,14 +4884,16 @@
       <c r="H24" s="45" t="s">
         <v>129</v>
       </c>
-      <c r="I24" s="45"/>
+      <c r="I24" s="45" t="s">
+        <v>175</v>
+      </c>
       <c r="J24" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="K24" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L24" s="74">
+      <c r="K24" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L24" s="64">
         <v>8</v>
       </c>
       <c r="M24" s="45">
@@ -4901,7 +4903,7 @@
       <c r="N24" s="45">
         <v>1050</v>
       </c>
-      <c r="O24" s="78" t="s">
+      <c r="O24" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P24" s="50">
@@ -4914,13 +4916,13 @@
       <c r="R24" s="46"/>
       <c r="S24" s="50"/>
     </row>
-    <row r="25" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="82"/>
+    <row r="25" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="72"/>
       <c r="B25" s="37">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="77" t="s">
+      <c r="C25" s="67" t="s">
         <v>174</v>
       </c>
       <c r="D25" s="48" t="s">
@@ -4944,7 +4946,7 @@
       <c r="J25" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="K25" s="71" t="s">
+      <c r="K25" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L25" s="48">
@@ -4962,18 +4964,18 @@
       <c r="Q25" s="51" t="s">
         <v>175</v>
       </c>
-      <c r="R25" s="81" t="s">
+      <c r="R25" s="71" t="s">
         <v>198</v>
       </c>
       <c r="S25" s="51"/>
     </row>
-    <row r="26" spans="1:19" s="84" customFormat="1" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="82"/>
+    <row r="26" spans="1:19" s="74" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="72"/>
       <c r="B26" s="37">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C26" s="66" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="45" t="s">
@@ -4997,10 +4999,10 @@
       <c r="J26" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="K26" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L26" s="74">
+      <c r="K26" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L26" s="64">
         <v>1</v>
       </c>
       <c r="M26" s="45">
@@ -5010,7 +5012,7 @@
       <c r="N26" s="45">
         <v>1040</v>
       </c>
-      <c r="O26" s="78" t="s">
+      <c r="O26" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P26" s="50">
@@ -5023,13 +5025,13 @@
       <c r="R26" s="46"/>
       <c r="S26" s="50"/>
     </row>
-    <row r="27" spans="1:19" s="84" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="82"/>
+    <row r="27" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="72"/>
       <c r="B27" s="37">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="77" t="s">
+      <c r="C27" s="67" t="s">
         <v>12</v>
       </c>
       <c r="D27" s="48" t="s">
@@ -5041,7 +5043,7 @@
       <c r="F27" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="80" t="s">
+      <c r="G27" s="70" t="s">
         <v>109</v>
       </c>
       <c r="H27" s="48" t="s">
@@ -5053,7 +5055,7 @@
       <c r="J27" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="K27" s="71" t="s">
+      <c r="K27" s="61" t="s">
         <v>164</v>
       </c>
       <c r="L27" s="48">
@@ -5066,7 +5068,7 @@
       <c r="N27" s="48">
         <v>3100</v>
       </c>
-      <c r="O27" s="79" t="s">
+      <c r="O27" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P27" s="51">
@@ -5079,13 +5081,13 @@
       <c r="R27" s="49"/>
       <c r="S27" s="51"/>
     </row>
-    <row r="28" spans="1:19" s="84" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="82"/>
+    <row r="28" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="72"/>
       <c r="B28" s="37">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="76" t="s">
+      <c r="C28" s="66" t="s">
         <v>12</v>
       </c>
       <c r="D28" s="45" t="s">
@@ -5109,10 +5111,10 @@
       <c r="J28" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="70" t="s">
+      <c r="K28" s="60" t="s">
         <v>165</v>
       </c>
-      <c r="L28" s="74">
+      <c r="L28" s="64">
         <v>2</v>
       </c>
       <c r="M28" s="45">
@@ -5122,7 +5124,7 @@
       <c r="N28" s="45">
         <v>2100</v>
       </c>
-      <c r="O28" s="78" t="s">
+      <c r="O28" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P28" s="50">
@@ -5135,13 +5137,13 @@
       <c r="R28" s="46"/>
       <c r="S28" s="50"/>
     </row>
-    <row r="29" spans="1:19" s="84" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="82"/>
+    <row r="29" spans="1:19" s="74" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="72"/>
       <c r="B29" s="37">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="77" t="s">
+      <c r="C29" s="67" t="s">
         <v>12</v>
       </c>
       <c r="D29" s="48" t="s">
@@ -5165,7 +5167,7 @@
       <c r="J29" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="K29" s="71" t="s">
+      <c r="K29" s="61" t="s">
         <v>166</v>
       </c>
       <c r="L29" s="48">
@@ -5178,7 +5180,7 @@
       <c r="N29" s="48">
         <v>4050</v>
       </c>
-      <c r="O29" s="79" t="s">
+      <c r="O29" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P29" s="51">
@@ -5191,13 +5193,13 @@
       <c r="R29" s="49"/>
       <c r="S29" s="51"/>
     </row>
-    <row r="30" spans="1:19" s="84" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="82"/>
+    <row r="30" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="72"/>
       <c r="B30" s="37">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="76" t="s">
+      <c r="C30" s="66" t="s">
         <v>12</v>
       </c>
       <c r="D30" s="45" t="s">
@@ -5221,10 +5223,10 @@
       <c r="J30" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="K30" s="70" t="s">
+      <c r="K30" s="60" t="s">
         <v>167</v>
       </c>
-      <c r="L30" s="74">
+      <c r="L30" s="64">
         <v>2</v>
       </c>
       <c r="M30" s="45">
@@ -5234,7 +5236,7 @@
       <c r="N30" s="45">
         <v>2100</v>
       </c>
-      <c r="O30" s="78" t="s">
+      <c r="O30" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P30" s="50">
@@ -5247,13 +5249,13 @@
       <c r="R30" s="46"/>
       <c r="S30" s="50"/>
     </row>
-    <row r="31" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="82"/>
+    <row r="31" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="72"/>
       <c r="B31" s="37">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="77" t="s">
+      <c r="C31" s="67" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="48" t="s">
@@ -5265,7 +5267,7 @@
       <c r="F31" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="G31" s="80" t="s">
+      <c r="G31" s="70" t="s">
         <v>113</v>
       </c>
       <c r="H31" s="48" t="s">
@@ -5277,7 +5279,7 @@
       <c r="J31" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="K31" s="71" t="s">
+      <c r="K31" s="61" t="s">
         <v>168</v>
       </c>
       <c r="L31" s="48">
@@ -5290,7 +5292,7 @@
       <c r="N31" s="48">
         <v>2100</v>
       </c>
-      <c r="O31" s="79" t="s">
+      <c r="O31" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P31" s="51">
@@ -5303,13 +5305,13 @@
       <c r="R31" s="49"/>
       <c r="S31" s="51"/>
     </row>
-    <row r="32" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="82"/>
+    <row r="32" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="72"/>
       <c r="B32" s="37">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="76" t="s">
+      <c r="C32" s="66" t="s">
         <v>12</v>
       </c>
       <c r="D32" s="45" t="s">
@@ -5333,10 +5335,10 @@
       <c r="J32" s="45" t="s">
         <v>151</v>
       </c>
-      <c r="K32" s="70" t="s">
+      <c r="K32" s="60" t="s">
         <v>169</v>
       </c>
-      <c r="L32" s="74">
+      <c r="L32" s="64">
         <v>1</v>
       </c>
       <c r="M32" s="45">
@@ -5346,7 +5348,7 @@
       <c r="N32" s="45">
         <v>1100</v>
       </c>
-      <c r="O32" s="78" t="s">
+      <c r="O32" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P32" s="50">
@@ -5359,13 +5361,13 @@
       <c r="R32" s="46"/>
       <c r="S32" s="50"/>
     </row>
-    <row r="33" spans="1:19" s="84" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="82"/>
+    <row r="33" spans="1:19" s="74" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="72"/>
       <c r="B33" s="37">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="67" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="48" t="s">
@@ -5389,7 +5391,7 @@
       <c r="J33" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="K33" s="71" t="s">
+      <c r="K33" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L33" s="48">
@@ -5402,7 +5404,7 @@
       <c r="N33" s="48">
         <v>1060</v>
       </c>
-      <c r="O33" s="79" t="s">
+      <c r="O33" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P33" s="51">
@@ -5415,13 +5417,13 @@
       <c r="R33" s="49"/>
       <c r="S33" s="51"/>
     </row>
-    <row r="34" spans="1:19" s="84" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="82"/>
+    <row r="34" spans="1:19" s="74" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="72"/>
       <c r="B34" s="37">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="66" t="s">
         <v>14</v>
       </c>
       <c r="D34" s="45" t="s">
@@ -5445,10 +5447,10 @@
       <c r="J34" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="K34" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L34" s="74">
+      <c r="K34" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L34" s="64">
         <v>1</v>
       </c>
       <c r="M34" s="45">
@@ -5458,7 +5460,7 @@
       <c r="N34" s="45">
         <v>1020</v>
       </c>
-      <c r="O34" s="78" t="s">
+      <c r="O34" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P34" s="50">
@@ -5468,18 +5470,18 @@
         <f t="shared" si="2"/>
         <v>3399.6600000000003</v>
       </c>
-      <c r="R34" s="85" t="s">
+      <c r="R34" s="75" t="s">
         <v>207</v>
       </c>
       <c r="S34" s="50"/>
     </row>
-    <row r="35" spans="1:19" s="84" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="82"/>
+    <row r="35" spans="1:19" s="74" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="72"/>
       <c r="B35" s="37">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="77" t="s">
+      <c r="C35" s="67" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="48" t="s">
@@ -5503,7 +5505,7 @@
       <c r="J35" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="K35" s="71" t="s">
+      <c r="K35" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L35" s="48">
@@ -5516,7 +5518,7 @@
       <c r="N35" s="48">
         <v>1030</v>
       </c>
-      <c r="O35" s="79" t="s">
+      <c r="O35" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P35" s="51">
@@ -5529,13 +5531,13 @@
       <c r="R35" s="49"/>
       <c r="S35" s="51"/>
     </row>
-    <row r="36" spans="1:19" s="84" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="82"/>
+    <row r="36" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="72"/>
       <c r="B36" s="37">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="76" t="s">
+      <c r="C36" s="66" t="s">
         <v>15</v>
       </c>
       <c r="D36" s="45" t="s">
@@ -5559,10 +5561,10 @@
       <c r="J36" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="K36" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L36" s="74">
+      <c r="K36" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L36" s="64">
         <v>1</v>
       </c>
       <c r="M36" s="45">
@@ -5572,7 +5574,7 @@
       <c r="N36" s="45">
         <v>1030</v>
       </c>
-      <c r="O36" s="78" t="s">
+      <c r="O36" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P36" s="50">
@@ -5585,13 +5587,13 @@
       <c r="R36" s="46"/>
       <c r="S36" s="50"/>
     </row>
-    <row r="37" spans="1:19" s="84" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="82"/>
+    <row r="37" spans="1:19" s="74" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="72"/>
       <c r="B37" s="37">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="67" t="s">
         <v>15</v>
       </c>
       <c r="D37" s="48" t="s">
@@ -5615,10 +5617,10 @@
       <c r="J37" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="K37" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="L37" s="75">
+      <c r="K37" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="L37" s="65">
         <v>1</v>
       </c>
       <c r="M37" s="48">
@@ -5628,7 +5630,7 @@
       <c r="N37" s="48">
         <v>1030</v>
       </c>
-      <c r="O37" s="79" t="s">
+      <c r="O37" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P37" s="51">
@@ -5653,19 +5655,19 @@
       <c r="I38" s="36"/>
       <c r="J38" s="35"/>
       <c r="K38" s="36"/>
-      <c r="L38" s="73"/>
+      <c r="L38" s="63"/>
       <c r="M38" s="36"/>
-      <c r="N38" s="65" t="s">
+      <c r="N38" s="99" t="s">
         <v>185</v>
       </c>
-      <c r="O38" s="66"/>
-      <c r="P38" s="66"/>
-      <c r="Q38" s="67">
+      <c r="O38" s="100"/>
+      <c r="P38" s="100"/>
+      <c r="Q38" s="57">
         <f>SUM(Q10:Q37)</f>
         <v>4373.9760000000006</v>
       </c>
-      <c r="R38" s="61"/>
-      <c r="S38" s="62"/>
+      <c r="R38" s="95"/>
+      <c r="S38" s="96"/>
     </row>
     <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
@@ -5681,17 +5683,17 @@
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
-      <c r="N39" s="65" t="s">
+      <c r="N39" s="99" t="s">
         <v>186</v>
       </c>
-      <c r="O39" s="66"/>
-      <c r="P39" s="66"/>
-      <c r="Q39" s="68">
+      <c r="O39" s="100"/>
+      <c r="P39" s="100"/>
+      <c r="Q39" s="58">
         <f>Q38/1000</f>
         <v>4.3739760000000008</v>
       </c>
-      <c r="R39" s="63"/>
-      <c r="S39" s="64"/>
+      <c r="R39" s="97"/>
+      <c r="S39" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5710,23 +5712,23 @@
     <hyperlink ref="O19" r:id="rId6" xr:uid="{01C9AFA9-A82C-4B2A-B412-FE864AFD6208}"/>
     <hyperlink ref="O20" r:id="rId7" xr:uid="{D6140372-66B5-4C88-8AC0-26723ECF074D}"/>
     <hyperlink ref="O22" r:id="rId8" xr:uid="{291EC59F-F9CF-4CC4-A9AB-FB3A19F9A6DC}"/>
-    <hyperlink ref="O24" r:id="rId9" xr:uid="{0E76850B-CFF0-4B75-B0CB-370E0522A449}"/>
-    <hyperlink ref="O26" r:id="rId10" xr:uid="{A6569824-1B8C-4A92-A7B4-EC57D1F57BC7}"/>
-    <hyperlink ref="O28" r:id="rId11" xr:uid="{F6948B1E-BBF9-4F1F-AFE8-42A86CD58DFC}"/>
-    <hyperlink ref="O29" r:id="rId12" xr:uid="{8059D976-5DB8-4771-8FA6-720530944C74}"/>
-    <hyperlink ref="O30" r:id="rId13" xr:uid="{DC146576-9860-4DD1-B7A8-7445E6025C6C}"/>
-    <hyperlink ref="O32" r:id="rId14" xr:uid="{AF7244EC-E5A8-4118-9DB1-DE0A8CCE4393}"/>
-    <hyperlink ref="O33" r:id="rId15" xr:uid="{D2593E23-2902-48EF-BA37-CE0AD4A2FBD5}"/>
-    <hyperlink ref="O34" r:id="rId16" xr:uid="{4EE3C90B-B4F8-4E04-A6C3-96CC793BE285}"/>
-    <hyperlink ref="O35" r:id="rId17" xr:uid="{53A45645-A0CE-4E03-AB60-06A9566B4DCC}"/>
-    <hyperlink ref="O36" r:id="rId18" xr:uid="{5E1BF6E0-9C81-4307-904E-B69F5151CE80}"/>
-    <hyperlink ref="O37" r:id="rId19" xr:uid="{EE60CBD9-0D2E-466F-BCDD-FB206A5D91BE}"/>
-    <hyperlink ref="O11" r:id="rId20" xr:uid="{AA83AC8C-2D7E-44ED-B5C6-E3D5D35A1359}"/>
-    <hyperlink ref="O15" r:id="rId21" xr:uid="{D09DE826-10C8-4AB8-B07C-53A7E34332C2}"/>
-    <hyperlink ref="O18" r:id="rId22" xr:uid="{14E75850-C7F5-4D4B-A751-DF3334752377}"/>
-    <hyperlink ref="O27" r:id="rId23" xr:uid="{08200A52-D7EF-4356-A07F-626BD40AAA3F}"/>
-    <hyperlink ref="O23" r:id="rId24" xr:uid="{0A068B27-7EBB-4604-8463-045AE13D012F}"/>
-    <hyperlink ref="O31" r:id="rId25" xr:uid="{222A17AA-674A-4697-B3A5-3F427A4B9885}"/>
+    <hyperlink ref="O26" r:id="rId9" xr:uid="{A6569824-1B8C-4A92-A7B4-EC57D1F57BC7}"/>
+    <hyperlink ref="O28" r:id="rId10" xr:uid="{F6948B1E-BBF9-4F1F-AFE8-42A86CD58DFC}"/>
+    <hyperlink ref="O29" r:id="rId11" xr:uid="{8059D976-5DB8-4771-8FA6-720530944C74}"/>
+    <hyperlink ref="O30" r:id="rId12" xr:uid="{DC146576-9860-4DD1-B7A8-7445E6025C6C}"/>
+    <hyperlink ref="O32" r:id="rId13" xr:uid="{AF7244EC-E5A8-4118-9DB1-DE0A8CCE4393}"/>
+    <hyperlink ref="O33" r:id="rId14" xr:uid="{D2593E23-2902-48EF-BA37-CE0AD4A2FBD5}"/>
+    <hyperlink ref="O34" r:id="rId15" xr:uid="{4EE3C90B-B4F8-4E04-A6C3-96CC793BE285}"/>
+    <hyperlink ref="O35" r:id="rId16" xr:uid="{53A45645-A0CE-4E03-AB60-06A9566B4DCC}"/>
+    <hyperlink ref="O36" r:id="rId17" xr:uid="{5E1BF6E0-9C81-4307-904E-B69F5151CE80}"/>
+    <hyperlink ref="O37" r:id="rId18" xr:uid="{EE60CBD9-0D2E-466F-BCDD-FB206A5D91BE}"/>
+    <hyperlink ref="O11" r:id="rId19" xr:uid="{AA83AC8C-2D7E-44ED-B5C6-E3D5D35A1359}"/>
+    <hyperlink ref="O15" r:id="rId20" xr:uid="{D09DE826-10C8-4AB8-B07C-53A7E34332C2}"/>
+    <hyperlink ref="O18" r:id="rId21" xr:uid="{14E75850-C7F5-4D4B-A751-DF3334752377}"/>
+    <hyperlink ref="O27" r:id="rId22" xr:uid="{08200A52-D7EF-4356-A07F-626BD40AAA3F}"/>
+    <hyperlink ref="O23" r:id="rId23" xr:uid="{0A068B27-7EBB-4604-8463-045AE13D012F}"/>
+    <hyperlink ref="O31" r:id="rId24" xr:uid="{222A17AA-674A-4697-B3A5-3F427A4B9885}"/>
+    <hyperlink ref="O24" r:id="rId25" xr:uid="{A7CDF02D-587A-47D6-83A7-F8F3A19B4AAE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId26"/>
@@ -5768,15 +5770,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="58"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="91"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="91"/>
+      <c r="S1" s="92"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -5826,7 +5828,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="59"/>
+      <c r="S3" s="93"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -5851,7 +5853,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="60"/>
+      <c r="S4" s="94"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -5876,7 +5878,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="60"/>
+      <c r="S5" s="94"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -5897,7 +5899,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="60"/>
+      <c r="S6" s="94"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -5918,7 +5920,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="60"/>
+      <c r="S7" s="94"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -5939,7 +5941,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="60"/>
+      <c r="S8" s="94"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -5970,13 +5972,13 @@
       <c r="J9" s="31" t="s">
         <v>137</v>
       </c>
-      <c r="K9" s="69" t="s">
+      <c r="K9" s="59" t="s">
         <v>177</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="M9" s="72" t="s">
+      <c r="M9" s="62" t="s">
         <v>208</v>
       </c>
       <c r="N9" s="31" t="s">
@@ -5998,13 +6000,13 @@
         <v>184</v>
       </c>
     </row>
-    <row r="10" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="82"/>
+    <row r="10" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="72"/>
       <c r="B10" s="37">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="76" t="s">
+      <c r="C10" s="66" t="s">
         <v>7</v>
       </c>
       <c r="D10" s="45" t="s">
@@ -6028,7 +6030,7 @@
       <c r="J10" s="45" t="s">
         <v>138</v>
       </c>
-      <c r="K10" s="70" t="s">
+      <c r="K10" s="60" t="s">
         <v>157</v>
       </c>
       <c r="L10" s="45">
@@ -6041,7 +6043,7 @@
       <c r="N10" s="45">
         <v>10100</v>
       </c>
-      <c r="O10" s="78" t="s">
+      <c r="O10" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P10" s="50">
@@ -6052,15 +6054,15 @@
         <v>131.29999999999998</v>
       </c>
       <c r="R10" s="46"/>
-      <c r="S10" s="83"/>
-    </row>
-    <row r="11" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="82"/>
+      <c r="S10" s="73"/>
+    </row>
+    <row r="11" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="72"/>
       <c r="B11" s="37">
         <f t="shared" ref="B11:B37" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="77" t="s">
+      <c r="C11" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D11" s="48" t="s">
@@ -6072,7 +6074,7 @@
       <c r="F11" s="48" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="80" t="s">
+      <c r="G11" s="70" t="s">
         <v>97</v>
       </c>
       <c r="H11" s="48" t="s">
@@ -6084,7 +6086,7 @@
       <c r="J11" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="K11" s="71" t="s">
+      <c r="K11" s="61" t="s">
         <v>158</v>
       </c>
       <c r="L11" s="48">
@@ -6097,7 +6099,7 @@
       <c r="N11" s="48">
         <v>10100</v>
       </c>
-      <c r="O11" s="79" t="s">
+      <c r="O11" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P11" s="51">
@@ -6110,13 +6112,13 @@
       <c r="R11" s="49"/>
       <c r="S11" s="51"/>
     </row>
-    <row r="12" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="82"/>
+    <row r="12" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="72"/>
       <c r="B12" s="37">
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="76" t="s">
+      <c r="C12" s="66" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="45" t="s">
@@ -6138,20 +6140,20 @@
       <c r="J12" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="K12" s="70" t="s">
+      <c r="K12" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="L12" s="74">
+      <c r="L12" s="64">
         <v>1</v>
       </c>
-      <c r="M12" s="74">
+      <c r="M12" s="64">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
       <c r="N12" s="45">
         <v>5100</v>
       </c>
-      <c r="O12" s="78" t="s">
+      <c r="O12" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P12" s="50">
@@ -6164,13 +6166,13 @@
       <c r="R12" s="46"/>
       <c r="S12" s="50"/>
     </row>
-    <row r="13" spans="1:19" s="84" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="82"/>
+    <row r="13" spans="1:19" s="74" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="72"/>
       <c r="B13" s="37">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="48" t="s">
@@ -6194,7 +6196,7 @@
       <c r="J13" s="48" t="s">
         <v>140</v>
       </c>
-      <c r="K13" s="71" t="s">
+      <c r="K13" s="61" t="s">
         <v>160</v>
       </c>
       <c r="L13" s="48">
@@ -6207,7 +6209,7 @@
       <c r="N13" s="48">
         <v>10100</v>
       </c>
-      <c r="O13" s="79" t="s">
+      <c r="O13" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P13" s="51">
@@ -6220,13 +6222,13 @@
       <c r="R13" s="49"/>
       <c r="S13" s="51"/>
     </row>
-    <row r="14" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="82"/>
+    <row r="14" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="72"/>
       <c r="B14" s="37">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="76" t="s">
+      <c r="C14" s="66" t="s">
         <v>7</v>
       </c>
       <c r="D14" s="45" t="s">
@@ -6250,20 +6252,20 @@
       <c r="J14" s="45" t="s">
         <v>141</v>
       </c>
-      <c r="K14" s="70" t="s">
+      <c r="K14" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="L14" s="74">
+      <c r="L14" s="64">
         <v>1</v>
       </c>
-      <c r="M14" s="74">
+      <c r="M14" s="64">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
       <c r="N14" s="45">
         <v>5100</v>
       </c>
-      <c r="O14" s="78" t="s">
+      <c r="O14" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P14" s="50">
@@ -6276,13 +6278,13 @@
       <c r="R14" s="46"/>
       <c r="S14" s="50"/>
     </row>
-    <row r="15" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="82"/>
+    <row r="15" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="72"/>
       <c r="B15" s="37">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="77" t="s">
+      <c r="C15" s="67" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="48" t="s">
@@ -6294,7 +6296,7 @@
       <c r="F15" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="80" t="s">
+      <c r="G15" s="70" t="s">
         <v>100</v>
       </c>
       <c r="H15" s="48" t="s">
@@ -6306,7 +6308,7 @@
       <c r="J15" s="48" t="s">
         <v>194</v>
       </c>
-      <c r="K15" s="71" t="s">
+      <c r="K15" s="61" t="s">
         <v>162</v>
       </c>
       <c r="L15" s="48">
@@ -6319,7 +6321,7 @@
       <c r="N15" s="48">
         <v>5100</v>
       </c>
-      <c r="O15" s="79" t="s">
+      <c r="O15" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P15" s="51">
@@ -6332,124 +6334,124 @@
       <c r="R15" s="49"/>
       <c r="S15" s="51"/>
     </row>
-    <row r="16" spans="1:19" s="94" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="86"/>
-      <c r="B16" s="87">
+    <row r="16" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="76">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="88" t="s">
+      <c r="C16" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="89" t="s">
+      <c r="D16" s="78" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="90" t="s">
+      <c r="E16" s="79" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="89" t="s">
+      <c r="F16" s="78" t="s">
         <v>79</v>
       </c>
-      <c r="G16" s="90" t="s">
+      <c r="G16" s="79" t="s">
         <v>101</v>
       </c>
-      <c r="H16" s="89" t="s">
+      <c r="H16" s="78" t="s">
         <v>122</v>
       </c>
-      <c r="I16" s="89"/>
-      <c r="J16" s="89" t="s">
+      <c r="I16" s="78"/>
+      <c r="J16" s="78" t="s">
         <v>142</v>
       </c>
-      <c r="K16" s="91" t="s">
+      <c r="K16" s="80" t="s">
         <v>163</v>
       </c>
-      <c r="L16" s="100">
+      <c r="L16" s="88">
         <v>1</v>
       </c>
-      <c r="M16" s="100">
+      <c r="M16" s="88">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="N16" s="89">
+      <c r="N16" s="78">
         <v>5100</v>
       </c>
-      <c r="O16" s="92" t="s">
+      <c r="O16" s="81" t="s">
         <v>190</v>
       </c>
-      <c r="P16" s="93">
+      <c r="P16" s="82">
         <v>1.0500000000000001E-2</v>
       </c>
-      <c r="Q16" s="93">
+      <c r="Q16" s="82">
         <f t="shared" si="2"/>
         <v>53.550000000000004</v>
       </c>
-      <c r="R16" s="90"/>
-      <c r="S16" s="93"/>
-    </row>
-    <row r="17" spans="1:19" s="94" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="86"/>
-      <c r="B17" s="87">
+      <c r="R16" s="79"/>
+      <c r="S16" s="82"/>
+    </row>
+    <row r="17" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="B17" s="76">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="95" t="s">
+      <c r="C17" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="96" t="s">
+      <c r="D17" s="84" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="97" t="s">
+      <c r="E17" s="85" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="96" t="s">
+      <c r="F17" s="84" t="s">
         <v>76</v>
       </c>
-      <c r="G17" s="97" t="s">
-        <v>175</v>
-      </c>
-      <c r="H17" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="I17" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="J17" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="K17" s="98" t="s">
-        <v>175</v>
-      </c>
-      <c r="L17" s="96">
+      <c r="G17" s="85" t="s">
+        <v>175</v>
+      </c>
+      <c r="H17" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="I17" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="J17" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="K17" s="86" t="s">
+        <v>175</v>
+      </c>
+      <c r="L17" s="84">
         <v>2</v>
       </c>
-      <c r="M17" s="96">
+      <c r="M17" s="84">
         <f t="shared" si="1"/>
         <v>10000</v>
       </c>
-      <c r="N17" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="O17" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="P17" s="99" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q17" s="99" t="s">
-        <v>175</v>
-      </c>
-      <c r="R17" s="101" t="s">
+      <c r="N17" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="O17" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="P17" s="87" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q17" s="87" t="s">
+        <v>175</v>
+      </c>
+      <c r="R17" s="89" t="s">
         <v>198</v>
       </c>
-      <c r="S17" s="99"/>
-    </row>
-    <row r="18" spans="1:19" s="84" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="82"/>
+      <c r="S17" s="87"/>
+    </row>
+    <row r="18" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="72"/>
       <c r="B18" s="37">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="76" t="s">
+      <c r="C18" s="66" t="s">
         <v>171</v>
       </c>
       <c r="D18" s="45" t="s">
@@ -6473,20 +6475,20 @@
       <c r="J18" s="45" t="s">
         <v>195</v>
       </c>
-      <c r="K18" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L18" s="74">
+      <c r="K18" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L18" s="64">
         <v>1</v>
       </c>
-      <c r="M18" s="74">
+      <c r="M18" s="64">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
       <c r="N18" s="45">
         <v>5050</v>
       </c>
-      <c r="O18" s="78" t="s">
+      <c r="O18" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P18" s="50">
@@ -6499,13 +6501,13 @@
       <c r="R18" s="46"/>
       <c r="S18" s="50"/>
     </row>
-    <row r="19" spans="1:19" s="84" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="82"/>
+    <row r="19" spans="1:19" s="74" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="72"/>
       <c r="B19" s="37">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="67" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="48" t="s">
@@ -6529,7 +6531,7 @@
       <c r="J19" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="K19" s="71" t="s">
+      <c r="K19" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L19" s="48">
@@ -6542,7 +6544,7 @@
       <c r="N19" s="48">
         <v>5050</v>
       </c>
-      <c r="O19" s="79" t="s">
+      <c r="O19" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P19" s="51">
@@ -6555,13 +6557,13 @@
       <c r="R19" s="49"/>
       <c r="S19" s="51"/>
     </row>
-    <row r="20" spans="1:19" s="84" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="82"/>
+    <row r="20" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="72"/>
       <c r="B20" s="37">
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="66" t="s">
         <v>172</v>
       </c>
       <c r="D20" s="45" t="s">
@@ -6585,20 +6587,20 @@
       <c r="J20" s="45" t="s">
         <v>144</v>
       </c>
-      <c r="K20" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L20" s="74">
+      <c r="K20" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L20" s="64">
         <v>1</v>
       </c>
-      <c r="M20" s="74">
+      <c r="M20" s="64">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
       <c r="N20" s="45">
         <v>5050</v>
       </c>
-      <c r="O20" s="78" t="s">
+      <c r="O20" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P20" s="50">
@@ -6611,70 +6613,70 @@
       <c r="R20" s="46"/>
       <c r="S20" s="50"/>
     </row>
-    <row r="21" spans="1:19" s="94" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="86"/>
-      <c r="B21" s="87">
+    <row r="21" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="76">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="95" t="s">
+      <c r="C21" s="83" t="s">
         <v>173</v>
       </c>
-      <c r="D21" s="96" t="s">
+      <c r="D21" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="E21" s="97" t="s">
+      <c r="E21" s="85" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="96" t="s">
+      <c r="F21" s="84" t="s">
         <v>189</v>
       </c>
-      <c r="G21" s="96" t="s">
+      <c r="G21" s="84" t="s">
         <v>82</v>
       </c>
-      <c r="H21" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="I21" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="J21" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="K21" s="98" t="s">
-        <v>175</v>
-      </c>
-      <c r="L21" s="96">
+      <c r="H21" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="I21" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="J21" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="K21" s="86" t="s">
+        <v>175</v>
+      </c>
+      <c r="L21" s="84">
         <v>1</v>
       </c>
-      <c r="M21" s="96">
+      <c r="M21" s="84">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="N21" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="O21" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="P21" s="99" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q21" s="99" t="s">
-        <v>175</v>
-      </c>
-      <c r="R21" s="101" t="s">
+      <c r="N21" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="O21" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="P21" s="87" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q21" s="87" t="s">
+        <v>175</v>
+      </c>
+      <c r="R21" s="89" t="s">
         <v>198</v>
       </c>
-      <c r="S21" s="99"/>
-    </row>
-    <row r="22" spans="1:19" s="84" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="82"/>
+      <c r="S21" s="87"/>
+    </row>
+    <row r="22" spans="1:19" s="74" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="72"/>
       <c r="B22" s="37">
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="76" t="s">
+      <c r="C22" s="66" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="45" t="s">
@@ -6698,20 +6700,20 @@
       <c r="J22" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="K22" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L22" s="74">
+      <c r="K22" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L22" s="64">
         <v>1</v>
       </c>
-      <c r="M22" s="74">
+      <c r="M22" s="64">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
       <c r="N22" s="45">
         <v>5050</v>
       </c>
-      <c r="O22" s="78" t="s">
+      <c r="O22" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P22" s="50">
@@ -6721,18 +6723,18 @@
         <f t="shared" si="2"/>
         <v>224.72499999999999</v>
       </c>
-      <c r="R22" s="85" t="s">
+      <c r="R22" s="75" t="s">
         <v>207</v>
       </c>
       <c r="S22" s="50"/>
     </row>
-    <row r="23" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="82"/>
+    <row r="23" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="72"/>
       <c r="B23" s="37">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="77" t="s">
+      <c r="C23" s="67" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="48" t="s">
@@ -6744,7 +6746,7 @@
       <c r="F23" s="48" t="s">
         <v>83</v>
       </c>
-      <c r="G23" s="80" t="s">
+      <c r="G23" s="70" t="s">
         <v>106</v>
       </c>
       <c r="H23" s="48" t="s">
@@ -6756,7 +6758,7 @@
       <c r="J23" s="48" t="s">
         <v>200</v>
       </c>
-      <c r="K23" s="71" t="s">
+      <c r="K23" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L23" s="48">
@@ -6769,7 +6771,7 @@
       <c r="N23" s="48">
         <v>5100</v>
       </c>
-      <c r="O23" s="79" t="s">
+      <c r="O23" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P23" s="51">
@@ -6782,13 +6784,13 @@
       <c r="R23" s="49"/>
       <c r="S23" s="51"/>
     </row>
-    <row r="24" spans="1:19" s="84" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="82"/>
+    <row r="24" spans="1:19" s="74" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="72"/>
       <c r="B24" s="37">
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="76" t="s">
+      <c r="C24" s="66" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="45" t="s">
@@ -6812,98 +6814,98 @@
       <c r="J24" s="45" t="s">
         <v>146</v>
       </c>
-      <c r="K24" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L24" s="74">
+      <c r="K24" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L24" s="64">
         <v>8</v>
       </c>
-      <c r="M24" s="74">
+      <c r="M24" s="64">
         <f t="shared" si="1"/>
         <v>40000</v>
       </c>
       <c r="N24" s="45">
         <v>40100</v>
       </c>
-      <c r="O24" s="78" t="s">
+      <c r="O24" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P24" s="50">
-        <v>3.39E-2</v>
+        <v>3.3799999999999997E-2</v>
       </c>
       <c r="Q24" s="50">
         <f t="shared" si="2"/>
-        <v>1359.3899999999999</v>
-      </c>
-      <c r="R24" s="85" t="s">
+        <v>1355.3799999999999</v>
+      </c>
+      <c r="R24" s="75" t="s">
         <v>207</v>
       </c>
       <c r="S24" s="50"/>
     </row>
-    <row r="25" spans="1:19" s="94" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="86"/>
-      <c r="B25" s="87">
+    <row r="25" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1"/>
+      <c r="B25" s="76">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="95" t="s">
+      <c r="C25" s="83" t="s">
         <v>174</v>
       </c>
-      <c r="D25" s="96" t="s">
+      <c r="D25" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="E25" s="97" t="s">
+      <c r="E25" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="F25" s="96" t="s">
+      <c r="F25" s="84" t="s">
         <v>189</v>
       </c>
-      <c r="G25" s="97" t="s">
-        <v>175</v>
-      </c>
-      <c r="H25" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="I25" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="J25" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="K25" s="98" t="s">
-        <v>175</v>
-      </c>
-      <c r="L25" s="96">
+      <c r="G25" s="85" t="s">
+        <v>175</v>
+      </c>
+      <c r="H25" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="I25" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="K25" s="86" t="s">
+        <v>175</v>
+      </c>
+      <c r="L25" s="84">
         <v>3</v>
       </c>
-      <c r="M25" s="96">
+      <c r="M25" s="84">
         <f t="shared" si="1"/>
         <v>15000</v>
       </c>
-      <c r="N25" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="O25" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="P25" s="99" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q25" s="99" t="s">
-        <v>175</v>
-      </c>
-      <c r="R25" s="101" t="s">
+      <c r="N25" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="O25" s="84" t="s">
+        <v>175</v>
+      </c>
+      <c r="P25" s="87" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q25" s="87" t="s">
+        <v>175</v>
+      </c>
+      <c r="R25" s="89" t="s">
         <v>198</v>
       </c>
-      <c r="S25" s="99"/>
-    </row>
-    <row r="26" spans="1:19" s="84" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="82"/>
+      <c r="S25" s="87"/>
+    </row>
+    <row r="26" spans="1:19" s="74" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="72"/>
       <c r="B26" s="37">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="C26" s="66" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="45" t="s">
@@ -6927,20 +6929,20 @@
       <c r="J26" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="K26" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L26" s="74">
+      <c r="K26" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L26" s="64">
         <v>1</v>
       </c>
-      <c r="M26" s="74">
+      <c r="M26" s="64">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
       <c r="N26" s="45">
         <v>5060</v>
       </c>
-      <c r="O26" s="78" t="s">
+      <c r="O26" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P26" s="50">
@@ -6953,13 +6955,13 @@
       <c r="R26" s="46"/>
       <c r="S26" s="50"/>
     </row>
-    <row r="27" spans="1:19" s="84" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="82"/>
+    <row r="27" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="72"/>
       <c r="B27" s="37">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="77" t="s">
+      <c r="C27" s="67" t="s">
         <v>12</v>
       </c>
       <c r="D27" s="48" t="s">
@@ -6971,7 +6973,7 @@
       <c r="F27" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="G27" s="80" t="s">
+      <c r="G27" s="70" t="s">
         <v>109</v>
       </c>
       <c r="H27" s="48" t="s">
@@ -6983,7 +6985,7 @@
       <c r="J27" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="K27" s="71" t="s">
+      <c r="K27" s="61" t="s">
         <v>164</v>
       </c>
       <c r="L27" s="48">
@@ -6996,7 +6998,7 @@
       <c r="N27" s="48">
         <v>15100</v>
       </c>
-      <c r="O27" s="79" t="s">
+      <c r="O27" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P27" s="51">
@@ -7009,13 +7011,13 @@
       <c r="R27" s="49"/>
       <c r="S27" s="51"/>
     </row>
-    <row r="28" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="82"/>
+    <row r="28" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="72"/>
       <c r="B28" s="37">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="76" t="s">
+      <c r="C28" s="66" t="s">
         <v>12</v>
       </c>
       <c r="D28" s="45" t="s">
@@ -7039,20 +7041,20 @@
       <c r="J28" s="45" t="s">
         <v>148</v>
       </c>
-      <c r="K28" s="70" t="s">
+      <c r="K28" s="60" t="s">
         <v>165</v>
       </c>
-      <c r="L28" s="74">
+      <c r="L28" s="64">
         <v>2</v>
       </c>
-      <c r="M28" s="74">
+      <c r="M28" s="64">
         <f t="shared" si="1"/>
         <v>10000</v>
       </c>
       <c r="N28" s="45">
         <v>10100</v>
       </c>
-      <c r="O28" s="78" t="s">
+      <c r="O28" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P28" s="50">
@@ -7065,13 +7067,13 @@
       <c r="R28" s="46"/>
       <c r="S28" s="50"/>
     </row>
-    <row r="29" spans="1:19" s="84" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="82"/>
+    <row r="29" spans="1:19" s="74" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="72"/>
       <c r="B29" s="37">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="77" t="s">
+      <c r="C29" s="67" t="s">
         <v>12</v>
       </c>
       <c r="D29" s="48" t="s">
@@ -7095,7 +7097,7 @@
       <c r="J29" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="K29" s="71" t="s">
+      <c r="K29" s="61" t="s">
         <v>166</v>
       </c>
       <c r="L29" s="48">
@@ -7108,7 +7110,7 @@
       <c r="N29" s="48">
         <v>20100</v>
       </c>
-      <c r="O29" s="79" t="s">
+      <c r="O29" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P29" s="51">
@@ -7118,74 +7120,74 @@
         <f t="shared" si="2"/>
         <v>110.55</v>
       </c>
-      <c r="R29" s="102" t="s">
+      <c r="R29" s="90" t="s">
         <v>207</v>
       </c>
       <c r="S29" s="51"/>
     </row>
-    <row r="30" spans="1:19" s="94" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="86"/>
-      <c r="B30" s="87">
+    <row r="30" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="B30" s="76">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="88" t="s">
+      <c r="C30" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="D30" s="89" t="s">
+      <c r="D30" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="E30" s="90" t="s">
+      <c r="E30" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="F30" s="89" t="s">
+      <c r="F30" s="78" t="s">
         <v>87</v>
       </c>
-      <c r="G30" s="90" t="s">
+      <c r="G30" s="79" t="s">
         <v>112</v>
       </c>
-      <c r="H30" s="89" t="s">
+      <c r="H30" s="78" t="s">
         <v>122</v>
       </c>
-      <c r="I30" s="89" t="s">
-        <v>175</v>
-      </c>
-      <c r="J30" s="89" t="s">
+      <c r="I30" s="78" t="s">
+        <v>175</v>
+      </c>
+      <c r="J30" s="78" t="s">
         <v>150</v>
       </c>
-      <c r="K30" s="91" t="s">
+      <c r="K30" s="80" t="s">
         <v>167</v>
       </c>
-      <c r="L30" s="100">
+      <c r="L30" s="88">
         <v>2</v>
       </c>
-      <c r="M30" s="100">
+      <c r="M30" s="88">
         <f t="shared" si="1"/>
         <v>10000</v>
       </c>
-      <c r="N30" s="89">
+      <c r="N30" s="78">
         <v>10100</v>
       </c>
-      <c r="O30" s="92" t="s">
+      <c r="O30" s="81" t="s">
         <v>190</v>
       </c>
-      <c r="P30" s="93">
+      <c r="P30" s="82">
         <v>5.9999999999999995E-4</v>
       </c>
-      <c r="Q30" s="93">
+      <c r="Q30" s="82">
         <f t="shared" si="2"/>
         <v>6.06</v>
       </c>
-      <c r="R30" s="90"/>
-      <c r="S30" s="93"/>
-    </row>
-    <row r="31" spans="1:19" s="84" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="82"/>
+      <c r="R30" s="79"/>
+      <c r="S30" s="82"/>
+    </row>
+    <row r="31" spans="1:19" s="74" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="72"/>
       <c r="B31" s="37">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="77" t="s">
+      <c r="C31" s="67" t="s">
         <v>12</v>
       </c>
       <c r="D31" s="48" t="s">
@@ -7197,7 +7199,7 @@
       <c r="F31" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="G31" s="80" t="s">
+      <c r="G31" s="70" t="s">
         <v>113</v>
       </c>
       <c r="H31" s="48" t="s">
@@ -7209,7 +7211,7 @@
       <c r="J31" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="K31" s="71" t="s">
+      <c r="K31" s="61" t="s">
         <v>168</v>
       </c>
       <c r="L31" s="48">
@@ -7222,7 +7224,7 @@
       <c r="N31" s="48">
         <v>10100</v>
       </c>
-      <c r="O31" s="79" t="s">
+      <c r="O31" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P31" s="51">
@@ -7235,69 +7237,69 @@
       <c r="R31" s="49"/>
       <c r="S31" s="51"/>
     </row>
-    <row r="32" spans="1:19" s="94" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="86"/>
-      <c r="B32" s="87">
+    <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+      <c r="B32" s="76">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="88" t="s">
+      <c r="C32" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="D32" s="89" t="s">
+      <c r="D32" s="78" t="s">
         <v>39</v>
       </c>
-      <c r="E32" s="90" t="s">
+      <c r="E32" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="F32" s="89" t="s">
+      <c r="F32" s="78" t="s">
         <v>87</v>
       </c>
-      <c r="G32" s="90" t="s">
+      <c r="G32" s="79" t="s">
         <v>114</v>
       </c>
-      <c r="H32" s="89" t="s">
+      <c r="H32" s="78" t="s">
         <v>122</v>
       </c>
-      <c r="I32" s="89" t="s">
-        <v>175</v>
-      </c>
-      <c r="J32" s="89" t="s">
+      <c r="I32" s="78" t="s">
+        <v>175</v>
+      </c>
+      <c r="J32" s="78" t="s">
         <v>151</v>
       </c>
-      <c r="K32" s="91" t="s">
+      <c r="K32" s="80" t="s">
         <v>169</v>
       </c>
-      <c r="L32" s="100">
+      <c r="L32" s="88">
         <v>1</v>
       </c>
-      <c r="M32" s="100">
+      <c r="M32" s="88">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
-      <c r="N32" s="89">
+      <c r="N32" s="78">
         <v>5100</v>
       </c>
-      <c r="O32" s="92" t="s">
+      <c r="O32" s="81" t="s">
         <v>190</v>
       </c>
-      <c r="P32" s="93">
+      <c r="P32" s="82">
         <v>1.1000000000000001E-3</v>
       </c>
-      <c r="Q32" s="93">
+      <c r="Q32" s="82">
         <f t="shared" si="2"/>
         <v>5.61</v>
       </c>
-      <c r="R32" s="90"/>
-      <c r="S32" s="93"/>
-    </row>
-    <row r="33" spans="1:19" s="84" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="82"/>
+      <c r="R32" s="79"/>
+      <c r="S32" s="82"/>
+    </row>
+    <row r="33" spans="1:19" s="74" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="72"/>
       <c r="B33" s="37">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="77" t="s">
+      <c r="C33" s="67" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="48" t="s">
@@ -7321,7 +7323,7 @@
       <c r="J33" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="K33" s="71" t="s">
+      <c r="K33" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L33" s="48">
@@ -7334,7 +7336,7 @@
       <c r="N33" s="48">
         <v>5060</v>
       </c>
-      <c r="O33" s="79" t="s">
+      <c r="O33" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P33" s="51">
@@ -7344,18 +7346,18 @@
         <f t="shared" si="2"/>
         <v>55.66</v>
       </c>
-      <c r="R33" s="102" t="s">
+      <c r="R33" s="90" t="s">
         <v>207</v>
       </c>
       <c r="S33" s="51"/>
     </row>
-    <row r="34" spans="1:19" s="84" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="82"/>
+    <row r="34" spans="1:19" s="74" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="72"/>
       <c r="B34" s="37">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="76" t="s">
+      <c r="C34" s="66" t="s">
         <v>14</v>
       </c>
       <c r="D34" s="45" t="s">
@@ -7379,20 +7381,20 @@
       <c r="J34" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="K34" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L34" s="74">
+      <c r="K34" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L34" s="64">
         <v>1</v>
       </c>
-      <c r="M34" s="74">
+      <c r="M34" s="64">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
       <c r="N34" s="45">
         <v>5020</v>
       </c>
-      <c r="O34" s="78" t="s">
+      <c r="O34" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P34" s="50">
@@ -7402,18 +7404,18 @@
         <f t="shared" si="2"/>
         <v>16731.66</v>
       </c>
-      <c r="R34" s="85" t="s">
+      <c r="R34" s="75" t="s">
         <v>207</v>
       </c>
       <c r="S34" s="50"/>
     </row>
-    <row r="35" spans="1:19" s="84" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="82"/>
+    <row r="35" spans="1:19" s="74" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="72"/>
       <c r="B35" s="37">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="77" t="s">
+      <c r="C35" s="67" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="48" t="s">
@@ -7437,7 +7439,7 @@
       <c r="J35" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="K35" s="71" t="s">
+      <c r="K35" s="61" t="s">
         <v>175</v>
       </c>
       <c r="L35" s="48">
@@ -7450,7 +7452,7 @@
       <c r="N35" s="48">
         <v>5030</v>
       </c>
-      <c r="O35" s="79" t="s">
+      <c r="O35" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P35" s="51">
@@ -7463,13 +7465,13 @@
       <c r="R35" s="49"/>
       <c r="S35" s="51"/>
     </row>
-    <row r="36" spans="1:19" s="84" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="82"/>
+    <row r="36" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="72"/>
       <c r="B36" s="37">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="76" t="s">
+      <c r="C36" s="66" t="s">
         <v>15</v>
       </c>
       <c r="D36" s="45" t="s">
@@ -7493,20 +7495,20 @@
       <c r="J36" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="K36" s="70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L36" s="74">
+      <c r="K36" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="L36" s="64">
         <v>1</v>
       </c>
-      <c r="M36" s="74">
+      <c r="M36" s="64">
         <f t="shared" si="1"/>
         <v>5000</v>
       </c>
       <c r="N36" s="45">
         <v>5030</v>
       </c>
-      <c r="O36" s="78" t="s">
+      <c r="O36" s="68" t="s">
         <v>190</v>
       </c>
       <c r="P36" s="50">
@@ -7519,13 +7521,13 @@
       <c r="R36" s="46"/>
       <c r="S36" s="50"/>
     </row>
-    <row r="37" spans="1:19" s="84" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="82"/>
+    <row r="37" spans="1:19" s="74" customFormat="1" ht="51.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="72"/>
       <c r="B37" s="37">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="77" t="s">
+      <c r="C37" s="67" t="s">
         <v>15</v>
       </c>
       <c r="D37" s="48" t="s">
@@ -7549,10 +7551,10 @@
       <c r="J37" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="K37" s="71" t="s">
-        <v>175</v>
-      </c>
-      <c r="L37" s="75">
+      <c r="K37" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="L37" s="65">
         <v>1</v>
       </c>
       <c r="M37" s="48">
@@ -7562,7 +7564,7 @@
       <c r="N37" s="48">
         <v>5030</v>
       </c>
-      <c r="O37" s="79" t="s">
+      <c r="O37" s="69" t="s">
         <v>190</v>
       </c>
       <c r="P37" s="51">
@@ -7572,7 +7574,7 @@
         <f t="shared" si="2"/>
         <v>482.88</v>
       </c>
-      <c r="R37" s="102" t="s">
+      <c r="R37" s="90" t="s">
         <v>207</v>
       </c>
       <c r="S37" s="51"/>
@@ -7589,19 +7591,19 @@
       <c r="I38" s="36"/>
       <c r="J38" s="35"/>
       <c r="K38" s="36"/>
-      <c r="L38" s="73"/>
+      <c r="L38" s="63"/>
       <c r="M38" s="36"/>
-      <c r="N38" s="65" t="s">
+      <c r="N38" s="99" t="s">
         <v>185</v>
       </c>
-      <c r="O38" s="66"/>
-      <c r="P38" s="66"/>
-      <c r="Q38" s="67">
+      <c r="O38" s="100"/>
+      <c r="P38" s="100"/>
+      <c r="Q38" s="57">
         <f>SUM(Q10:Q37)</f>
-        <v>22345.593000000001</v>
-      </c>
-      <c r="R38" s="61"/>
-      <c r="S38" s="62"/>
+        <v>22341.583000000002</v>
+      </c>
+      <c r="R38" s="95"/>
+      <c r="S38" s="96"/>
     </row>
     <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
@@ -7617,17 +7619,17 @@
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
       <c r="M39" s="10"/>
-      <c r="N39" s="65" t="s">
+      <c r="N39" s="99" t="s">
         <v>186</v>
       </c>
-      <c r="O39" s="66"/>
-      <c r="P39" s="66"/>
-      <c r="Q39" s="68">
+      <c r="O39" s="100"/>
+      <c r="P39" s="100"/>
+      <c r="Q39" s="58">
         <f>Q38/5000</f>
-        <v>4.4691185999999998</v>
-      </c>
-      <c r="R39" s="63"/>
-      <c r="S39" s="64"/>
+        <v>4.4683166000000005</v>
+      </c>
+      <c r="R39" s="97"/>
+      <c r="S39" s="98"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7646,23 +7648,23 @@
     <hyperlink ref="O19" r:id="rId6" xr:uid="{40AEB6AF-FCDB-44C1-B55B-A304F2627966}"/>
     <hyperlink ref="O20" r:id="rId7" xr:uid="{9E1DD19F-B45C-4CDE-9989-31677A614178}"/>
     <hyperlink ref="O22" r:id="rId8" xr:uid="{35777828-0BDC-48AA-A7A9-F7A8E68DFC26}"/>
-    <hyperlink ref="O24" r:id="rId9" xr:uid="{5CD4A5D1-3DC1-4B93-BCCA-A57711DF38DC}"/>
-    <hyperlink ref="O26" r:id="rId10" xr:uid="{0BDEA316-3B63-4D49-9D0B-7021045EBBE5}"/>
-    <hyperlink ref="O28" r:id="rId11" xr:uid="{1523C799-6FEE-4401-A618-3E502F6F9661}"/>
-    <hyperlink ref="O29" r:id="rId12" xr:uid="{3579D16A-9554-4C96-A78D-4EBCFC22394C}"/>
-    <hyperlink ref="O30" r:id="rId13" xr:uid="{7CC93527-36AE-4B54-8A34-060899F9BB0D}"/>
-    <hyperlink ref="O32" r:id="rId14" xr:uid="{F3232C60-6B76-473D-BE7C-30490F8E18AA}"/>
-    <hyperlink ref="O33" r:id="rId15" xr:uid="{5620C896-CB50-42C1-8CF0-C1EADAFD27BA}"/>
-    <hyperlink ref="O34" r:id="rId16" xr:uid="{27697CEB-6113-4379-BDD1-7CDFD0532B59}"/>
-    <hyperlink ref="O35" r:id="rId17" xr:uid="{97CB3E7D-20AC-45B9-AA15-E43B6BEC306A}"/>
-    <hyperlink ref="O36" r:id="rId18" xr:uid="{7AF0D8E2-A85E-4CF9-AD09-51055F4EF83F}"/>
-    <hyperlink ref="O37" r:id="rId19" xr:uid="{E8B87B67-1FF7-45CD-9DC7-EA9C3E13540C}"/>
-    <hyperlink ref="O11" r:id="rId20" xr:uid="{5A201E8F-2E21-44D4-8CDC-FD8E0483CF34}"/>
-    <hyperlink ref="O15" r:id="rId21" xr:uid="{7B80FD7F-D0A3-44ED-AE03-9CB51C53039D}"/>
-    <hyperlink ref="O18" r:id="rId22" xr:uid="{574FAF25-A4CC-47F8-B01A-F676D49910B1}"/>
-    <hyperlink ref="O27" r:id="rId23" xr:uid="{876685AA-B7B9-4DBF-9393-87B286924B65}"/>
-    <hyperlink ref="O23" r:id="rId24" xr:uid="{EE9BB81B-9F6D-4F63-8883-F592F27BDEF8}"/>
-    <hyperlink ref="O31" r:id="rId25" xr:uid="{3901A63A-9B6B-4EDA-ACAA-05296D06C4C2}"/>
+    <hyperlink ref="O26" r:id="rId9" xr:uid="{0BDEA316-3B63-4D49-9D0B-7021045EBBE5}"/>
+    <hyperlink ref="O28" r:id="rId10" xr:uid="{1523C799-6FEE-4401-A618-3E502F6F9661}"/>
+    <hyperlink ref="O29" r:id="rId11" xr:uid="{3579D16A-9554-4C96-A78D-4EBCFC22394C}"/>
+    <hyperlink ref="O30" r:id="rId12" xr:uid="{7CC93527-36AE-4B54-8A34-060899F9BB0D}"/>
+    <hyperlink ref="O32" r:id="rId13" xr:uid="{F3232C60-6B76-473D-BE7C-30490F8E18AA}"/>
+    <hyperlink ref="O33" r:id="rId14" xr:uid="{5620C896-CB50-42C1-8CF0-C1EADAFD27BA}"/>
+    <hyperlink ref="O34" r:id="rId15" xr:uid="{27697CEB-6113-4379-BDD1-7CDFD0532B59}"/>
+    <hyperlink ref="O35" r:id="rId16" xr:uid="{97CB3E7D-20AC-45B9-AA15-E43B6BEC306A}"/>
+    <hyperlink ref="O36" r:id="rId17" xr:uid="{7AF0D8E2-A85E-4CF9-AD09-51055F4EF83F}"/>
+    <hyperlink ref="O37" r:id="rId18" xr:uid="{E8B87B67-1FF7-45CD-9DC7-EA9C3E13540C}"/>
+    <hyperlink ref="O11" r:id="rId19" xr:uid="{5A201E8F-2E21-44D4-8CDC-FD8E0483CF34}"/>
+    <hyperlink ref="O15" r:id="rId20" xr:uid="{7B80FD7F-D0A3-44ED-AE03-9CB51C53039D}"/>
+    <hyperlink ref="O18" r:id="rId21" xr:uid="{574FAF25-A4CC-47F8-B01A-F676D49910B1}"/>
+    <hyperlink ref="O27" r:id="rId22" xr:uid="{876685AA-B7B9-4DBF-9393-87B286924B65}"/>
+    <hyperlink ref="O23" r:id="rId23" xr:uid="{EE9BB81B-9F6D-4F63-8883-F592F27BDEF8}"/>
+    <hyperlink ref="O31" r:id="rId24" xr:uid="{3901A63A-9B6B-4EDA-ACAA-05296D06C4C2}"/>
+    <hyperlink ref="O24" r:id="rId25" xr:uid="{7ECCFD6F-457A-4166-85DB-52AD29C48721}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId26"/>
